--- a/public/assets/files/sub-growsers-template.xlsx
+++ b/public/assets/files/sub-growsers-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\GitHub\stts\public\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED1CBB4-03E3-4CBE-8411-70BFD5C06AEE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AD677C-E4C3-4D89-8241-84439FC38743}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9570" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="449">
   <si>
     <t>ID</t>
   </si>
@@ -1371,75 +1371,6 @@
   </si>
   <si>
     <t>Village</t>
-  </si>
-  <si>
-    <t>F001</t>
-  </si>
-  <si>
-    <t>Nantabo hildah</t>
-  </si>
-  <si>
-    <t>Pre basic</t>
-  </si>
-  <si>
-    <t>Naro/2543</t>
-  </si>
-  <si>
-    <t>Kawanda</t>
-  </si>
-  <si>
-    <t>073456789</t>
-  </si>
-  <si>
-    <t>0.0001</t>
-  </si>
-  <si>
-    <t>0.555</t>
-  </si>
-  <si>
-    <t>Wakiso</t>
-  </si>
-  <si>
-    <t>wakiso</t>
-  </si>
-  <si>
-    <t>F002</t>
-  </si>
-  <si>
-    <t>Mbabazi Isaac</t>
-  </si>
-  <si>
-    <t>Naro/435</t>
-  </si>
-  <si>
-    <t>073456665</t>
-  </si>
-  <si>
-    <t>0.6663</t>
-  </si>
-  <si>
-    <t>F003</t>
-  </si>
-  <si>
-    <t>Priscillah Amokol</t>
-  </si>
-  <si>
-    <t>Naro/876</t>
-  </si>
-  <si>
-    <t>Kwanda</t>
-  </si>
-  <si>
-    <t>073456456</t>
-  </si>
-  <si>
-    <t>0.0003</t>
-  </si>
-  <si>
-    <t>0.6637</t>
-  </si>
-  <si>
-    <t>Masaka</t>
   </si>
   <si>
     <t>Crop and variety</t>
@@ -7506,7 +7437,7 @@
         <v>435</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>471</v>
+        <v>448</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>436</v>
@@ -7547,156 +7478,33 @@
       <c r="Q1" s="4"/>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="C2" s="4">
-        <v>10</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="H2" s="2">
-        <v>46042</v>
-      </c>
-      <c r="I2" s="4">
-        <v>24</v>
-      </c>
-      <c r="J2" s="4">
-        <v>200</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>457</v>
-      </c>
+      <c r="H2" s="2"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
       <c r="Q2" s="4"/>
     </row>
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="C3" s="4">
-        <v>25</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="H3" s="2">
-        <v>45930</v>
-      </c>
-      <c r="I3" s="4">
-        <v>20</v>
-      </c>
-      <c r="J3" s="4">
-        <v>2880</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>457</v>
-      </c>
+      <c r="H3" s="2"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
       <c r="Q3" s="4"/>
     </row>
     <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="C4" s="4">
-        <v>23</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="H4" s="2">
-        <v>45692</v>
-      </c>
-      <c r="I4" s="4">
-        <v>10</v>
-      </c>
-      <c r="J4" s="4">
-        <v>1000</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>470</v>
-      </c>
+      <c r="H4" s="2"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
       <c r="Q4" s="4"/>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">

--- a/public/assets/files/sub-growsers-template.xlsx
+++ b/public/assets/files/sub-growsers-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\GitHub\stts\public\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AD677C-E4C3-4D89-8241-84439FC38743}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909DD897-90FF-418D-AF17-D98C03FC8362}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9570" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
